--- a/labs/lab-07-dashboard-to-presentation/data/Northstar_Work_Orders.xlsx
+++ b/labs/lab-07-dashboard-to-presentation/data/Northstar_Work_Orders.xlsx
@@ -844,7 +844,7 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>Northstar Facilities - fictional</t>
+          <t>Northstar Water Services - fictional water-pipe maintenance and service company</t>
         </is>
       </c>
     </row>
@@ -1004,7 +1004,7 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>HVAC</t>
+          <t>Leak Repair</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
@@ -1042,7 +1042,7 @@
       </c>
       <c r="M2" s="2" t="inlineStr">
         <is>
-          <t>HVAC scheduled or reactive task 001</t>
+          <t>Leak Repair scheduled or reactive task 001</t>
         </is>
       </c>
     </row>
@@ -1059,7 +1059,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>HVAC</t>
+          <t>Leak Repair</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
@@ -1097,7 +1097,7 @@
       </c>
       <c r="M3" s="2" t="inlineStr">
         <is>
-          <t>HVAC scheduled or reactive task 002</t>
+          <t>Leak Repair scheduled or reactive task 002</t>
         </is>
       </c>
     </row>
@@ -1114,7 +1114,7 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>HVAC</t>
+          <t>Leak Repair</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
@@ -1150,7 +1150,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>HVAC scheduled or reactive task 003</t>
+          <t>Leak Repair scheduled or reactive task 003</t>
         </is>
       </c>
     </row>
@@ -1167,7 +1167,7 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>HVAC</t>
+          <t>Leak Repair</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
@@ -1203,7 +1203,7 @@
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>HVAC scheduled or reactive task 004</t>
+          <t>Leak Repair scheduled or reactive task 004</t>
         </is>
       </c>
     </row>
@@ -1220,7 +1220,7 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>Electrical</t>
+          <t>Valve Repair</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
@@ -1256,7 +1256,7 @@
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>Electrical scheduled or reactive task 005</t>
+          <t>Valve Repair scheduled or reactive task 005</t>
         </is>
       </c>
     </row>
@@ -1273,7 +1273,7 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>Electrical</t>
+          <t>Valve Repair</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
@@ -1311,7 +1311,7 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>Electrical scheduled or reactive task 006</t>
+          <t>Valve Repair scheduled or reactive task 006</t>
         </is>
       </c>
     </row>
@@ -1328,7 +1328,7 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>Electrical</t>
+          <t>Valve Repair</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
@@ -1366,7 +1366,7 @@
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>Electrical scheduled or reactive task 007</t>
+          <t>Valve Repair scheduled or reactive task 007</t>
         </is>
       </c>
     </row>
@@ -1383,7 +1383,7 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>Electrical</t>
+          <t>Valve Repair</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
@@ -1419,7 +1419,7 @@
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>Electrical scheduled or reactive task 008</t>
+          <t>Valve Repair scheduled or reactive task 008</t>
         </is>
       </c>
     </row>
@@ -1436,7 +1436,7 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>Plumbing</t>
+          <t>Pipe Replacement</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
@@ -1472,7 +1472,7 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>Plumbing scheduled or reactive task 009</t>
+          <t>Pipe Replacement scheduled or reactive task 009</t>
         </is>
       </c>
     </row>
@@ -1489,7 +1489,7 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>Plumbing</t>
+          <t>Pipe Replacement</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
@@ -1525,7 +1525,7 @@
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>Plumbing scheduled or reactive task 010</t>
+          <t>Pipe Replacement scheduled or reactive task 010</t>
         </is>
       </c>
     </row>
@@ -1542,7 +1542,7 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>Plumbing</t>
+          <t>Pipe Replacement</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
@@ -1580,7 +1580,7 @@
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>Plumbing scheduled or reactive task 011</t>
+          <t>Pipe Replacement scheduled or reactive task 011</t>
         </is>
       </c>
     </row>
@@ -1597,7 +1597,7 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>Plumbing</t>
+          <t>Pipe Replacement</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
@@ -1635,7 +1635,7 @@
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>Plumbing scheduled or reactive task 012</t>
+          <t>Pipe Replacement scheduled or reactive task 012</t>
         </is>
       </c>
     </row>
@@ -1652,7 +1652,7 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>Fire Safety</t>
+          <t>Pump Service</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
@@ -1684,7 +1684,7 @@
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>Fire Safety scheduled or reactive task 013</t>
+          <t>Pump Service scheduled or reactive task 013</t>
         </is>
       </c>
     </row>
@@ -1701,7 +1701,7 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>Fire Safety</t>
+          <t>Pump Service</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
@@ -1737,7 +1737,7 @@
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>Fire Safety scheduled or reactive task 014</t>
+          <t>Pump Service scheduled or reactive task 014</t>
         </is>
       </c>
     </row>
@@ -1754,7 +1754,7 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>Fire Safety</t>
+          <t>Pump Service</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
@@ -1790,7 +1790,7 @@
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>Fire Safety scheduled or reactive task 015</t>
+          <t>Pump Service scheduled or reactive task 015</t>
         </is>
       </c>
     </row>
@@ -1807,7 +1807,7 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>Fire Safety</t>
+          <t>Pump Service</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
@@ -1845,7 +1845,7 @@
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>Fire Safety scheduled or reactive task 016</t>
+          <t>Pump Service scheduled or reactive task 016</t>
         </is>
       </c>
     </row>
@@ -1862,7 +1862,7 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>General Repair</t>
+          <t>Meter Service</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
@@ -1900,7 +1900,7 @@
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>General Repair scheduled or reactive task 017</t>
+          <t>Meter Service scheduled or reactive task 017</t>
         </is>
       </c>
     </row>
@@ -1917,7 +1917,7 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>General Repair</t>
+          <t>Meter Service</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
@@ -1953,7 +1953,7 @@
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>General Repair scheduled or reactive task 018</t>
+          <t>Meter Service scheduled or reactive task 018</t>
         </is>
       </c>
     </row>
@@ -1970,7 +1970,7 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>General Repair</t>
+          <t>Meter Service</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
@@ -2006,7 +2006,7 @@
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>General Repair scheduled or reactive task 019</t>
+          <t>Meter Service scheduled or reactive task 019</t>
         </is>
       </c>
     </row>
@@ -2023,7 +2023,7 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>General Repair</t>
+          <t>Meter Service</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
@@ -2059,7 +2059,7 @@
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>General Repair scheduled or reactive task 020</t>
+          <t>Meter Service scheduled or reactive task 020</t>
         </is>
       </c>
     </row>
@@ -2076,7 +2076,7 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>HVAC</t>
+          <t>Leak Repair</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
@@ -2114,7 +2114,7 @@
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>HVAC scheduled or reactive task 021</t>
+          <t>Leak Repair scheduled or reactive task 021</t>
         </is>
       </c>
     </row>
@@ -2131,7 +2131,7 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>HVAC</t>
+          <t>Leak Repair</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
@@ -2169,7 +2169,7 @@
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>HVAC scheduled or reactive task 022</t>
+          <t>Leak Repair scheduled or reactive task 022</t>
         </is>
       </c>
     </row>
@@ -2186,7 +2186,7 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>HVAC</t>
+          <t>Leak Repair</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
@@ -2222,7 +2222,7 @@
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>HVAC scheduled or reactive task 023</t>
+          <t>Leak Repair scheduled or reactive task 023</t>
         </is>
       </c>
     </row>
@@ -2239,7 +2239,7 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>HVAC</t>
+          <t>Leak Repair</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
@@ -2275,7 +2275,7 @@
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>HVAC scheduled or reactive task 024</t>
+          <t>Leak Repair scheduled or reactive task 024</t>
         </is>
       </c>
     </row>
@@ -2292,7 +2292,7 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>Electrical</t>
+          <t>Valve Repair</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
@@ -2324,7 +2324,7 @@
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>Electrical scheduled or reactive task 025</t>
+          <t>Valve Repair scheduled or reactive task 025</t>
         </is>
       </c>
     </row>
@@ -2341,7 +2341,7 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>Electrical</t>
+          <t>Valve Repair</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
@@ -2379,7 +2379,7 @@
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>Electrical scheduled or reactive task 026</t>
+          <t>Valve Repair scheduled or reactive task 026</t>
         </is>
       </c>
     </row>
@@ -2396,7 +2396,7 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>Electrical</t>
+          <t>Valve Repair</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
@@ -2434,7 +2434,7 @@
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>Electrical scheduled or reactive task 027</t>
+          <t>Valve Repair scheduled or reactive task 027</t>
         </is>
       </c>
     </row>
@@ -2451,7 +2451,7 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>Electrical</t>
+          <t>Valve Repair</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
@@ -2487,7 +2487,7 @@
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>Electrical scheduled or reactive task 028</t>
+          <t>Valve Repair scheduled or reactive task 028</t>
         </is>
       </c>
     </row>
@@ -2504,7 +2504,7 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>Plumbing</t>
+          <t>Pipe Replacement</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
@@ -2540,7 +2540,7 @@
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>Plumbing scheduled or reactive task 029</t>
+          <t>Pipe Replacement scheduled or reactive task 029</t>
         </is>
       </c>
     </row>
@@ -2557,7 +2557,7 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>Plumbing</t>
+          <t>Pipe Replacement</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
@@ -2593,7 +2593,7 @@
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>Plumbing scheduled or reactive task 030</t>
+          <t>Pipe Replacement scheduled or reactive task 030</t>
         </is>
       </c>
     </row>
@@ -2610,7 +2610,7 @@
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>Plumbing</t>
+          <t>Pipe Replacement</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
@@ -2648,7 +2648,7 @@
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>Plumbing scheduled or reactive task 031</t>
+          <t>Pipe Replacement scheduled or reactive task 031</t>
         </is>
       </c>
     </row>
@@ -2665,7 +2665,7 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>Plumbing</t>
+          <t>Pipe Replacement</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
@@ -2703,7 +2703,7 @@
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>Plumbing scheduled or reactive task 032</t>
+          <t>Pipe Replacement scheduled or reactive task 032</t>
         </is>
       </c>
     </row>
@@ -2720,7 +2720,7 @@
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>Fire Safety</t>
+          <t>Pump Service</t>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr">
@@ -2756,7 +2756,7 @@
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>Fire Safety scheduled or reactive task 033</t>
+          <t>Pump Service scheduled or reactive task 033</t>
         </is>
       </c>
     </row>
@@ -2773,7 +2773,7 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>Fire Safety</t>
+          <t>Pump Service</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
@@ -2809,7 +2809,7 @@
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>Fire Safety scheduled or reactive task 034</t>
+          <t>Pump Service scheduled or reactive task 034</t>
         </is>
       </c>
     </row>
@@ -2826,7 +2826,7 @@
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>Fire Safety</t>
+          <t>Pump Service</t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr">
@@ -2862,7 +2862,7 @@
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>Fire Safety scheduled or reactive task 035</t>
+          <t>Pump Service scheduled or reactive task 035</t>
         </is>
       </c>
     </row>
@@ -2879,7 +2879,7 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>Fire Safety</t>
+          <t>Pump Service</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
@@ -2917,7 +2917,7 @@
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>Fire Safety scheduled or reactive task 036</t>
+          <t>Pump Service scheduled or reactive task 036</t>
         </is>
       </c>
     </row>
@@ -2934,7 +2934,7 @@
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>General Repair</t>
+          <t>Meter Service</t>
         </is>
       </c>
       <c r="D38" s="2" t="inlineStr">
@@ -2972,7 +2972,7 @@
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>General Repair scheduled or reactive task 037</t>
+          <t>Meter Service scheduled or reactive task 037</t>
         </is>
       </c>
     </row>
@@ -2989,7 +2989,7 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>General Repair</t>
+          <t>Meter Service</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
@@ -3025,7 +3025,7 @@
       </c>
       <c r="M39" s="2" t="inlineStr">
         <is>
-          <t>General Repair scheduled or reactive task 038</t>
+          <t>Meter Service scheduled or reactive task 038</t>
         </is>
       </c>
     </row>
@@ -3042,7 +3042,7 @@
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>General Repair</t>
+          <t>Meter Service</t>
         </is>
       </c>
       <c r="D40" s="2" t="inlineStr">
@@ -3078,7 +3078,7 @@
       </c>
       <c r="M40" s="2" t="inlineStr">
         <is>
-          <t>General Repair scheduled or reactive task 039</t>
+          <t>Meter Service scheduled or reactive task 039</t>
         </is>
       </c>
     </row>
@@ -3095,7 +3095,7 @@
       </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>General Repair</t>
+          <t>Meter Service</t>
         </is>
       </c>
       <c r="D41" s="2" t="inlineStr">
@@ -3131,7 +3131,7 @@
       </c>
       <c r="M41" s="2" t="inlineStr">
         <is>
-          <t>General Repair scheduled or reactive task 040</t>
+          <t>Meter Service scheduled or reactive task 040</t>
         </is>
       </c>
     </row>
@@ -3148,7 +3148,7 @@
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>HVAC</t>
+          <t>Leak Repair</t>
         </is>
       </c>
       <c r="D42" s="2" t="inlineStr">
@@ -3186,7 +3186,7 @@
       </c>
       <c r="M42" s="2" t="inlineStr">
         <is>
-          <t>HVAC scheduled or reactive task 041</t>
+          <t>Leak Repair scheduled or reactive task 041</t>
         </is>
       </c>
     </row>
@@ -3203,7 +3203,7 @@
       </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t>HVAC</t>
+          <t>Leak Repair</t>
         </is>
       </c>
       <c r="D43" s="2" t="inlineStr">
@@ -3241,7 +3241,7 @@
       </c>
       <c r="M43" s="2" t="inlineStr">
         <is>
-          <t>HVAC scheduled or reactive task 042</t>
+          <t>Leak Repair scheduled or reactive task 042</t>
         </is>
       </c>
     </row>
@@ -3258,7 +3258,7 @@
       </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>HVAC</t>
+          <t>Leak Repair</t>
         </is>
       </c>
       <c r="D44" s="2" t="inlineStr">
@@ -3294,7 +3294,7 @@
       </c>
       <c r="M44" s="2" t="inlineStr">
         <is>
-          <t>HVAC scheduled or reactive task 043</t>
+          <t>Leak Repair scheduled or reactive task 043</t>
         </is>
       </c>
     </row>
@@ -3311,7 +3311,7 @@
       </c>
       <c r="C45" s="2" t="inlineStr">
         <is>
-          <t>HVAC</t>
+          <t>Leak Repair</t>
         </is>
       </c>
       <c r="D45" s="2" t="inlineStr">
@@ -3347,7 +3347,7 @@
       </c>
       <c r="M45" s="2" t="inlineStr">
         <is>
-          <t>HVAC scheduled or reactive task 044</t>
+          <t>Leak Repair scheduled or reactive task 044</t>
         </is>
       </c>
     </row>
@@ -3364,7 +3364,7 @@
       </c>
       <c r="C46" s="2" t="inlineStr">
         <is>
-          <t>Electrical</t>
+          <t>Valve Repair</t>
         </is>
       </c>
       <c r="D46" s="2" t="inlineStr">
@@ -3400,7 +3400,7 @@
       </c>
       <c r="M46" s="2" t="inlineStr">
         <is>
-          <t>Electrical scheduled or reactive task 045</t>
+          <t>Valve Repair scheduled or reactive task 045</t>
         </is>
       </c>
     </row>
@@ -3417,7 +3417,7 @@
       </c>
       <c r="C47" s="2" t="inlineStr">
         <is>
-          <t>Electrical</t>
+          <t>Valve Repair</t>
         </is>
       </c>
       <c r="D47" s="2" t="inlineStr">
@@ -3455,7 +3455,7 @@
       </c>
       <c r="M47" s="2" t="inlineStr">
         <is>
-          <t>Electrical scheduled or reactive task 046</t>
+          <t>Valve Repair scheduled or reactive task 046</t>
         </is>
       </c>
     </row>
@@ -3472,7 +3472,7 @@
       </c>
       <c r="C48" s="2" t="inlineStr">
         <is>
-          <t>Electrical</t>
+          <t>Valve Repair</t>
         </is>
       </c>
       <c r="D48" s="2" t="inlineStr">
@@ -3510,7 +3510,7 @@
       </c>
       <c r="M48" s="2" t="inlineStr">
         <is>
-          <t>Electrical scheduled or reactive task 047</t>
+          <t>Valve Repair scheduled or reactive task 047</t>
         </is>
       </c>
     </row>
@@ -3527,7 +3527,7 @@
       </c>
       <c r="C49" s="2" t="inlineStr">
         <is>
-          <t>Electrical</t>
+          <t>Valve Repair</t>
         </is>
       </c>
       <c r="D49" s="2" t="inlineStr">
@@ -3563,7 +3563,7 @@
       </c>
       <c r="M49" s="2" t="inlineStr">
         <is>
-          <t>Electrical scheduled or reactive task 048</t>
+          <t>Valve Repair scheduled or reactive task 048</t>
         </is>
       </c>
     </row>
@@ -3580,7 +3580,7 @@
       </c>
       <c r="C50" s="2" t="inlineStr">
         <is>
-          <t>Plumbing</t>
+          <t>Pipe Replacement</t>
         </is>
       </c>
       <c r="D50" s="2" t="inlineStr">
@@ -3612,7 +3612,7 @@
       </c>
       <c r="M50" s="2" t="inlineStr">
         <is>
-          <t>Plumbing scheduled or reactive task 049</t>
+          <t>Pipe Replacement scheduled or reactive task 049</t>
         </is>
       </c>
     </row>
@@ -3629,7 +3629,7 @@
       </c>
       <c r="C51" s="2" t="inlineStr">
         <is>
-          <t>Plumbing</t>
+          <t>Pipe Replacement</t>
         </is>
       </c>
       <c r="D51" s="2" t="inlineStr">
@@ -3665,7 +3665,7 @@
       </c>
       <c r="M51" s="2" t="inlineStr">
         <is>
-          <t>Plumbing scheduled or reactive task 050</t>
+          <t>Pipe Replacement scheduled or reactive task 050</t>
         </is>
       </c>
     </row>
@@ -3682,7 +3682,7 @@
       </c>
       <c r="C52" s="2" t="inlineStr">
         <is>
-          <t>Plumbing</t>
+          <t>Pipe Replacement</t>
         </is>
       </c>
       <c r="D52" s="2" t="inlineStr">
@@ -3720,7 +3720,7 @@
       </c>
       <c r="M52" s="2" t="inlineStr">
         <is>
-          <t>Plumbing scheduled or reactive task 051</t>
+          <t>Pipe Replacement scheduled or reactive task 051</t>
         </is>
       </c>
     </row>
@@ -3737,7 +3737,7 @@
       </c>
       <c r="C53" s="2" t="inlineStr">
         <is>
-          <t>Plumbing</t>
+          <t>Pipe Replacement</t>
         </is>
       </c>
       <c r="D53" s="2" t="inlineStr">
@@ -3775,7 +3775,7 @@
       </c>
       <c r="M53" s="2" t="inlineStr">
         <is>
-          <t>Plumbing scheduled or reactive task 052</t>
+          <t>Pipe Replacement scheduled or reactive task 052</t>
         </is>
       </c>
     </row>
@@ -3792,7 +3792,7 @@
       </c>
       <c r="C54" s="2" t="inlineStr">
         <is>
-          <t>Fire Safety</t>
+          <t>Pump Service</t>
         </is>
       </c>
       <c r="D54" s="2" t="inlineStr">
@@ -3828,7 +3828,7 @@
       </c>
       <c r="M54" s="2" t="inlineStr">
         <is>
-          <t>Fire Safety scheduled or reactive task 053</t>
+          <t>Pump Service scheduled or reactive task 053</t>
         </is>
       </c>
     </row>
@@ -3845,7 +3845,7 @@
       </c>
       <c r="C55" s="2" t="inlineStr">
         <is>
-          <t>Fire Safety</t>
+          <t>Pump Service</t>
         </is>
       </c>
       <c r="D55" s="2" t="inlineStr">
@@ -3881,7 +3881,7 @@
       </c>
       <c r="M55" s="2" t="inlineStr">
         <is>
-          <t>Fire Safety scheduled or reactive task 054</t>
+          <t>Pump Service scheduled or reactive task 054</t>
         </is>
       </c>
     </row>
@@ -3898,7 +3898,7 @@
       </c>
       <c r="C56" s="2" t="inlineStr">
         <is>
-          <t>Fire Safety</t>
+          <t>Pump Service</t>
         </is>
       </c>
       <c r="D56" s="2" t="inlineStr">
@@ -3934,7 +3934,7 @@
       </c>
       <c r="M56" s="2" t="inlineStr">
         <is>
-          <t>Fire Safety scheduled or reactive task 055</t>
+          <t>Pump Service scheduled or reactive task 055</t>
         </is>
       </c>
     </row>
@@ -3951,7 +3951,7 @@
       </c>
       <c r="C57" s="2" t="inlineStr">
         <is>
-          <t>Fire Safety</t>
+          <t>Pump Service</t>
         </is>
       </c>
       <c r="D57" s="2" t="inlineStr">
@@ -3989,7 +3989,7 @@
       </c>
       <c r="M57" s="2" t="inlineStr">
         <is>
-          <t>Fire Safety scheduled or reactive task 056</t>
+          <t>Pump Service scheduled or reactive task 056</t>
         </is>
       </c>
     </row>
@@ -4006,7 +4006,7 @@
       </c>
       <c r="C58" s="2" t="inlineStr">
         <is>
-          <t>General Repair</t>
+          <t>Meter Service</t>
         </is>
       </c>
       <c r="D58" s="2" t="inlineStr">
@@ -4044,7 +4044,7 @@
       </c>
       <c r="M58" s="2" t="inlineStr">
         <is>
-          <t>General Repair scheduled or reactive task 057</t>
+          <t>Meter Service scheduled or reactive task 057</t>
         </is>
       </c>
     </row>
@@ -4061,7 +4061,7 @@
       </c>
       <c r="C59" s="2" t="inlineStr">
         <is>
-          <t>General Repair</t>
+          <t>Meter Service</t>
         </is>
       </c>
       <c r="D59" s="2" t="inlineStr">
@@ -4097,7 +4097,7 @@
       </c>
       <c r="M59" s="2" t="inlineStr">
         <is>
-          <t>General Repair scheduled or reactive task 058</t>
+          <t>Meter Service scheduled or reactive task 058</t>
         </is>
       </c>
     </row>
@@ -4114,7 +4114,7 @@
       </c>
       <c r="C60" s="2" t="inlineStr">
         <is>
-          <t>General Repair</t>
+          <t>Meter Service</t>
         </is>
       </c>
       <c r="D60" s="2" t="inlineStr">
@@ -4150,7 +4150,7 @@
       </c>
       <c r="M60" s="2" t="inlineStr">
         <is>
-          <t>General Repair scheduled or reactive task 059</t>
+          <t>Meter Service scheduled or reactive task 059</t>
         </is>
       </c>
     </row>
@@ -4167,7 +4167,7 @@
       </c>
       <c r="C61" s="2" t="inlineStr">
         <is>
-          <t>General Repair</t>
+          <t>Meter Service</t>
         </is>
       </c>
       <c r="D61" s="2" t="inlineStr">
@@ -4203,7 +4203,7 @@
       </c>
       <c r="M61" s="2" t="inlineStr">
         <is>
-          <t>General Repair scheduled or reactive task 060</t>
+          <t>Meter Service scheduled or reactive task 060</t>
         </is>
       </c>
     </row>
@@ -4220,7 +4220,7 @@
       </c>
       <c r="C62" s="2" t="inlineStr">
         <is>
-          <t>HVAC</t>
+          <t>Leak Repair</t>
         </is>
       </c>
       <c r="D62" s="2" t="inlineStr">
@@ -4258,7 +4258,7 @@
       </c>
       <c r="M62" s="2" t="inlineStr">
         <is>
-          <t>HVAC scheduled or reactive task 061</t>
+          <t>Leak Repair scheduled or reactive task 061</t>
         </is>
       </c>
     </row>
@@ -4275,7 +4275,7 @@
       </c>
       <c r="C63" s="2" t="inlineStr">
         <is>
-          <t>HVAC</t>
+          <t>Leak Repair</t>
         </is>
       </c>
       <c r="D63" s="2" t="inlineStr">
@@ -4313,7 +4313,7 @@
       </c>
       <c r="M63" s="2" t="inlineStr">
         <is>
-          <t>HVAC scheduled or reactive task 062</t>
+          <t>Leak Repair scheduled or reactive task 062</t>
         </is>
       </c>
     </row>
@@ -4330,7 +4330,7 @@
       </c>
       <c r="C64" s="2" t="inlineStr">
         <is>
-          <t>HVAC</t>
+          <t>Leak Repair</t>
         </is>
       </c>
       <c r="D64" s="2" t="inlineStr">
@@ -4366,7 +4366,7 @@
       </c>
       <c r="M64" s="2" t="inlineStr">
         <is>
-          <t>HVAC scheduled or reactive task 063</t>
+          <t>Leak Repair scheduled or reactive task 063</t>
         </is>
       </c>
     </row>
@@ -4383,7 +4383,7 @@
       </c>
       <c r="C65" s="2" t="inlineStr">
         <is>
-          <t>HVAC</t>
+          <t>Leak Repair</t>
         </is>
       </c>
       <c r="D65" s="2" t="inlineStr">
@@ -4419,7 +4419,7 @@
       </c>
       <c r="M65" s="2" t="inlineStr">
         <is>
-          <t>HVAC scheduled or reactive task 064</t>
+          <t>Leak Repair scheduled or reactive task 064</t>
         </is>
       </c>
     </row>
@@ -4436,7 +4436,7 @@
       </c>
       <c r="C66" s="2" t="inlineStr">
         <is>
-          <t>Electrical</t>
+          <t>Valve Repair</t>
         </is>
       </c>
       <c r="D66" s="2" t="inlineStr">
@@ -4472,7 +4472,7 @@
       </c>
       <c r="M66" s="2" t="inlineStr">
         <is>
-          <t>Electrical scheduled or reactive task 065</t>
+          <t>Valve Repair scheduled or reactive task 065</t>
         </is>
       </c>
     </row>
@@ -4489,7 +4489,7 @@
       </c>
       <c r="C67" s="2" t="inlineStr">
         <is>
-          <t>Electrical</t>
+          <t>Valve Repair</t>
         </is>
       </c>
       <c r="D67" s="2" t="inlineStr">
@@ -4527,7 +4527,7 @@
       </c>
       <c r="M67" s="2" t="inlineStr">
         <is>
-          <t>Electrical scheduled or reactive task 066</t>
+          <t>Valve Repair scheduled or reactive task 066</t>
         </is>
       </c>
     </row>
@@ -4544,7 +4544,7 @@
       </c>
       <c r="C68" s="2" t="inlineStr">
         <is>
-          <t>Electrical</t>
+          <t>Valve Repair</t>
         </is>
       </c>
       <c r="D68" s="2" t="inlineStr">
@@ -4582,7 +4582,7 @@
       </c>
       <c r="M68" s="2" t="inlineStr">
         <is>
-          <t>Electrical scheduled or reactive task 067</t>
+          <t>Valve Repair scheduled or reactive task 067</t>
         </is>
       </c>
     </row>
@@ -4599,7 +4599,7 @@
       </c>
       <c r="C69" s="2" t="inlineStr">
         <is>
-          <t>Electrical</t>
+          <t>Valve Repair</t>
         </is>
       </c>
       <c r="D69" s="2" t="inlineStr">
@@ -4635,7 +4635,7 @@
       </c>
       <c r="M69" s="2" t="inlineStr">
         <is>
-          <t>Electrical scheduled or reactive task 068</t>
+          <t>Valve Repair scheduled or reactive task 068</t>
         </is>
       </c>
     </row>
@@ -4652,7 +4652,7 @@
       </c>
       <c r="C70" s="2" t="inlineStr">
         <is>
-          <t>Plumbing</t>
+          <t>Pipe Replacement</t>
         </is>
       </c>
       <c r="D70" s="2" t="inlineStr">
@@ -4688,7 +4688,7 @@
       </c>
       <c r="M70" s="2" t="inlineStr">
         <is>
-          <t>Plumbing scheduled or reactive task 069</t>
+          <t>Pipe Replacement scheduled or reactive task 069</t>
         </is>
       </c>
     </row>
@@ -4705,7 +4705,7 @@
       </c>
       <c r="C71" s="2" t="inlineStr">
         <is>
-          <t>Plumbing</t>
+          <t>Pipe Replacement</t>
         </is>
       </c>
       <c r="D71" s="2" t="inlineStr">
@@ -4741,7 +4741,7 @@
       </c>
       <c r="M71" s="2" t="inlineStr">
         <is>
-          <t>Plumbing scheduled or reactive task 070</t>
+          <t>Pipe Replacement scheduled or reactive task 070</t>
         </is>
       </c>
     </row>
@@ -4758,7 +4758,7 @@
       </c>
       <c r="C72" s="2" t="inlineStr">
         <is>
-          <t>Plumbing</t>
+          <t>Pipe Replacement</t>
         </is>
       </c>
       <c r="D72" s="2" t="inlineStr">
@@ -4796,7 +4796,7 @@
       </c>
       <c r="M72" s="2" t="inlineStr">
         <is>
-          <t>Plumbing scheduled or reactive task 071</t>
+          <t>Pipe Replacement scheduled or reactive task 071</t>
         </is>
       </c>
     </row>
@@ -4813,7 +4813,7 @@
       </c>
       <c r="C73" s="2" t="inlineStr">
         <is>
-          <t>Plumbing</t>
+          <t>Pipe Replacement</t>
         </is>
       </c>
       <c r="D73" s="2" t="inlineStr">
@@ -4851,7 +4851,7 @@
       </c>
       <c r="M73" s="2" t="inlineStr">
         <is>
-          <t>Plumbing scheduled or reactive task 072</t>
+          <t>Pipe Replacement scheduled or reactive task 072</t>
         </is>
       </c>
     </row>
@@ -4868,7 +4868,7 @@
       </c>
       <c r="C74" s="2" t="inlineStr">
         <is>
-          <t>Fire Safety</t>
+          <t>Pump Service</t>
         </is>
       </c>
       <c r="D74" s="2" t="inlineStr">
@@ -4900,7 +4900,7 @@
       </c>
       <c r="M74" s="2" t="inlineStr">
         <is>
-          <t>Fire Safety scheduled or reactive task 073</t>
+          <t>Pump Service scheduled or reactive task 073</t>
         </is>
       </c>
     </row>
@@ -4917,7 +4917,7 @@
       </c>
       <c r="C75" s="2" t="inlineStr">
         <is>
-          <t>Fire Safety</t>
+          <t>Pump Service</t>
         </is>
       </c>
       <c r="D75" s="2" t="inlineStr">
@@ -4953,7 +4953,7 @@
       </c>
       <c r="M75" s="2" t="inlineStr">
         <is>
-          <t>Fire Safety scheduled or reactive task 074</t>
+          <t>Pump Service scheduled or reactive task 074</t>
         </is>
       </c>
     </row>
@@ -4970,7 +4970,7 @@
       </c>
       <c r="C76" s="2" t="inlineStr">
         <is>
-          <t>Fire Safety</t>
+          <t>Pump Service</t>
         </is>
       </c>
       <c r="D76" s="2" t="inlineStr">
@@ -5006,7 +5006,7 @@
       </c>
       <c r="M76" s="2" t="inlineStr">
         <is>
-          <t>Fire Safety scheduled or reactive task 075</t>
+          <t>Pump Service scheduled or reactive task 075</t>
         </is>
       </c>
     </row>
@@ -5023,7 +5023,7 @@
       </c>
       <c r="C77" s="2" t="inlineStr">
         <is>
-          <t>Fire Safety</t>
+          <t>Pump Service</t>
         </is>
       </c>
       <c r="D77" s="2" t="inlineStr">
@@ -5061,7 +5061,7 @@
       </c>
       <c r="M77" s="2" t="inlineStr">
         <is>
-          <t>Fire Safety scheduled or reactive task 076</t>
+          <t>Pump Service scheduled or reactive task 076</t>
         </is>
       </c>
     </row>
@@ -5078,7 +5078,7 @@
       </c>
       <c r="C78" s="2" t="inlineStr">
         <is>
-          <t>General Repair</t>
+          <t>Meter Service</t>
         </is>
       </c>
       <c r="D78" s="2" t="inlineStr">
@@ -5116,7 +5116,7 @@
       </c>
       <c r="M78" s="2" t="inlineStr">
         <is>
-          <t>General Repair scheduled or reactive task 077</t>
+          <t>Meter Service scheduled or reactive task 077</t>
         </is>
       </c>
     </row>
@@ -5133,7 +5133,7 @@
       </c>
       <c r="C79" s="2" t="inlineStr">
         <is>
-          <t>General Repair</t>
+          <t>Meter Service</t>
         </is>
       </c>
       <c r="D79" s="2" t="inlineStr">
@@ -5169,7 +5169,7 @@
       </c>
       <c r="M79" s="2" t="inlineStr">
         <is>
-          <t>General Repair scheduled or reactive task 078</t>
+          <t>Meter Service scheduled or reactive task 078</t>
         </is>
       </c>
     </row>
@@ -5186,7 +5186,7 @@
       </c>
       <c r="C80" s="2" t="inlineStr">
         <is>
-          <t>General Repair</t>
+          <t>Meter Service</t>
         </is>
       </c>
       <c r="D80" s="2" t="inlineStr">
@@ -5222,7 +5222,7 @@
       </c>
       <c r="M80" s="2" t="inlineStr">
         <is>
-          <t>General Repair scheduled or reactive task 079</t>
+          <t>Meter Service scheduled or reactive task 079</t>
         </is>
       </c>
     </row>
@@ -5239,7 +5239,7 @@
       </c>
       <c r="C81" s="2" t="inlineStr">
         <is>
-          <t>General Repair</t>
+          <t>Meter Service</t>
         </is>
       </c>
       <c r="D81" s="2" t="inlineStr">
@@ -5275,7 +5275,7 @@
       </c>
       <c r="M81" s="2" t="inlineStr">
         <is>
-          <t>General Repair scheduled or reactive task 080</t>
+          <t>Meter Service scheduled or reactive task 080</t>
         </is>
       </c>
     </row>
@@ -5292,7 +5292,7 @@
       </c>
       <c r="C82" s="2" t="inlineStr">
         <is>
-          <t>HVAC</t>
+          <t>Leak Repair</t>
         </is>
       </c>
       <c r="D82" s="2" t="inlineStr">
@@ -5330,7 +5330,7 @@
       </c>
       <c r="M82" s="2" t="inlineStr">
         <is>
-          <t>HVAC scheduled or reactive task 081</t>
+          <t>Leak Repair scheduled or reactive task 081</t>
         </is>
       </c>
     </row>
@@ -5347,7 +5347,7 @@
       </c>
       <c r="C83" s="2" t="inlineStr">
         <is>
-          <t>HVAC</t>
+          <t>Leak Repair</t>
         </is>
       </c>
       <c r="D83" s="2" t="inlineStr">
@@ -5385,7 +5385,7 @@
       </c>
       <c r="M83" s="2" t="inlineStr">
         <is>
-          <t>HVAC scheduled or reactive task 082</t>
+          <t>Leak Repair scheduled or reactive task 082</t>
         </is>
       </c>
     </row>
@@ -5402,7 +5402,7 @@
       </c>
       <c r="C84" s="2" t="inlineStr">
         <is>
-          <t>HVAC</t>
+          <t>Leak Repair</t>
         </is>
       </c>
       <c r="D84" s="2" t="inlineStr">
@@ -5438,7 +5438,7 @@
       </c>
       <c r="M84" s="2" t="inlineStr">
         <is>
-          <t>HVAC scheduled or reactive task 083</t>
+          <t>Leak Repair scheduled or reactive task 083</t>
         </is>
       </c>
     </row>
@@ -5455,7 +5455,7 @@
       </c>
       <c r="C85" s="2" t="inlineStr">
         <is>
-          <t>HVAC</t>
+          <t>Leak Repair</t>
         </is>
       </c>
       <c r="D85" s="2" t="inlineStr">
@@ -5491,7 +5491,7 @@
       </c>
       <c r="M85" s="2" t="inlineStr">
         <is>
-          <t>HVAC scheduled or reactive task 084</t>
+          <t>Leak Repair scheduled or reactive task 084</t>
         </is>
       </c>
     </row>
@@ -5508,7 +5508,7 @@
       </c>
       <c r="C86" s="2" t="inlineStr">
         <is>
-          <t>Electrical</t>
+          <t>Valve Repair</t>
         </is>
       </c>
       <c r="D86" s="2" t="inlineStr">
@@ -5540,7 +5540,7 @@
       </c>
       <c r="M86" s="2" t="inlineStr">
         <is>
-          <t>Electrical scheduled or reactive task 085</t>
+          <t>Valve Repair scheduled or reactive task 085</t>
         </is>
       </c>
     </row>
@@ -5557,7 +5557,7 @@
       </c>
       <c r="C87" s="2" t="inlineStr">
         <is>
-          <t>Electrical</t>
+          <t>Valve Repair</t>
         </is>
       </c>
       <c r="D87" s="2" t="inlineStr">
@@ -5595,7 +5595,7 @@
       </c>
       <c r="M87" s="2" t="inlineStr">
         <is>
-          <t>Electrical scheduled or reactive task 086</t>
+          <t>Valve Repair scheduled or reactive task 086</t>
         </is>
       </c>
     </row>
@@ -5612,7 +5612,7 @@
       </c>
       <c r="C88" s="2" t="inlineStr">
         <is>
-          <t>Electrical</t>
+          <t>Valve Repair</t>
         </is>
       </c>
       <c r="D88" s="2" t="inlineStr">
@@ -5650,7 +5650,7 @@
       </c>
       <c r="M88" s="2" t="inlineStr">
         <is>
-          <t>Electrical scheduled or reactive task 087</t>
+          <t>Valve Repair scheduled or reactive task 087</t>
         </is>
       </c>
     </row>
@@ -5667,7 +5667,7 @@
       </c>
       <c r="C89" s="2" t="inlineStr">
         <is>
-          <t>Electrical</t>
+          <t>Valve Repair</t>
         </is>
       </c>
       <c r="D89" s="2" t="inlineStr">
@@ -5703,7 +5703,7 @@
       </c>
       <c r="M89" s="2" t="inlineStr">
         <is>
-          <t>Electrical scheduled or reactive task 088</t>
+          <t>Valve Repair scheduled or reactive task 088</t>
         </is>
       </c>
     </row>
@@ -5720,7 +5720,7 @@
       </c>
       <c r="C90" s="2" t="inlineStr">
         <is>
-          <t>Plumbing</t>
+          <t>Pipe Replacement</t>
         </is>
       </c>
       <c r="D90" s="2" t="inlineStr">
@@ -5756,7 +5756,7 @@
       </c>
       <c r="M90" s="2" t="inlineStr">
         <is>
-          <t>Plumbing scheduled or reactive task 089</t>
+          <t>Pipe Replacement scheduled or reactive task 089</t>
         </is>
       </c>
     </row>
@@ -5773,7 +5773,7 @@
       </c>
       <c r="C91" s="2" t="inlineStr">
         <is>
-          <t>Plumbing</t>
+          <t>Pipe Replacement</t>
         </is>
       </c>
       <c r="D91" s="2" t="inlineStr">
@@ -5809,7 +5809,7 @@
       </c>
       <c r="M91" s="2" t="inlineStr">
         <is>
-          <t>Plumbing scheduled or reactive task 090</t>
+          <t>Pipe Replacement scheduled or reactive task 090</t>
         </is>
       </c>
     </row>
@@ -5826,7 +5826,7 @@
       </c>
       <c r="C92" s="2" t="inlineStr">
         <is>
-          <t>Plumbing</t>
+          <t>Pipe Replacement</t>
         </is>
       </c>
       <c r="D92" s="2" t="inlineStr">
@@ -5864,7 +5864,7 @@
       </c>
       <c r="M92" s="2" t="inlineStr">
         <is>
-          <t>Plumbing scheduled or reactive task 091</t>
+          <t>Pipe Replacement scheduled or reactive task 091</t>
         </is>
       </c>
     </row>
@@ -5881,7 +5881,7 @@
       </c>
       <c r="C93" s="2" t="inlineStr">
         <is>
-          <t>Plumbing</t>
+          <t>Pipe Replacement</t>
         </is>
       </c>
       <c r="D93" s="2" t="inlineStr">
@@ -5919,7 +5919,7 @@
       </c>
       <c r="M93" s="2" t="inlineStr">
         <is>
-          <t>Plumbing scheduled or reactive task 092</t>
+          <t>Pipe Replacement scheduled or reactive task 092</t>
         </is>
       </c>
     </row>
@@ -5936,7 +5936,7 @@
       </c>
       <c r="C94" s="2" t="inlineStr">
         <is>
-          <t>Fire Safety</t>
+          <t>Pump Service</t>
         </is>
       </c>
       <c r="D94" s="2" t="inlineStr">
@@ -5972,7 +5972,7 @@
       </c>
       <c r="M94" s="2" t="inlineStr">
         <is>
-          <t>Fire Safety scheduled or reactive task 093</t>
+          <t>Pump Service scheduled or reactive task 093</t>
         </is>
       </c>
     </row>
@@ -5989,7 +5989,7 @@
       </c>
       <c r="C95" s="2" t="inlineStr">
         <is>
-          <t>Fire Safety</t>
+          <t>Pump Service</t>
         </is>
       </c>
       <c r="D95" s="2" t="inlineStr">
@@ -6025,7 +6025,7 @@
       </c>
       <c r="M95" s="2" t="inlineStr">
         <is>
-          <t>Fire Safety scheduled or reactive task 094</t>
+          <t>Pump Service scheduled or reactive task 094</t>
         </is>
       </c>
     </row>
@@ -6042,7 +6042,7 @@
       </c>
       <c r="C96" s="2" t="inlineStr">
         <is>
-          <t>Fire Safety</t>
+          <t>Pump Service</t>
         </is>
       </c>
       <c r="D96" s="2" t="inlineStr">
@@ -6078,7 +6078,7 @@
       </c>
       <c r="M96" s="2" t="inlineStr">
         <is>
-          <t>Fire Safety scheduled or reactive task 095</t>
+          <t>Pump Service scheduled or reactive task 095</t>
         </is>
       </c>
     </row>
@@ -6095,7 +6095,7 @@
       </c>
       <c r="C97" s="2" t="inlineStr">
         <is>
-          <t>Fire Safety</t>
+          <t>Pump Service</t>
         </is>
       </c>
       <c r="D97" s="2" t="inlineStr">
@@ -6133,7 +6133,7 @@
       </c>
       <c r="M97" s="2" t="inlineStr">
         <is>
-          <t>Fire Safety scheduled or reactive task 096</t>
+          <t>Pump Service scheduled or reactive task 096</t>
         </is>
       </c>
     </row>
@@ -6150,7 +6150,7 @@
       </c>
       <c r="C98" s="2" t="inlineStr">
         <is>
-          <t>General Repair</t>
+          <t>Meter Service</t>
         </is>
       </c>
       <c r="D98" s="2" t="inlineStr">
@@ -6188,7 +6188,7 @@
       </c>
       <c r="M98" s="2" t="inlineStr">
         <is>
-          <t>General Repair scheduled or reactive task 097</t>
+          <t>Meter Service scheduled or reactive task 097</t>
         </is>
       </c>
     </row>
@@ -6205,7 +6205,7 @@
       </c>
       <c r="C99" s="2" t="inlineStr">
         <is>
-          <t>General Repair</t>
+          <t>Meter Service</t>
         </is>
       </c>
       <c r="D99" s="2" t="inlineStr">
@@ -6241,7 +6241,7 @@
       </c>
       <c r="M99" s="2" t="inlineStr">
         <is>
-          <t>General Repair scheduled or reactive task 098</t>
+          <t>Meter Service scheduled or reactive task 098</t>
         </is>
       </c>
     </row>
@@ -6258,7 +6258,7 @@
       </c>
       <c r="C100" s="2" t="inlineStr">
         <is>
-          <t>General Repair</t>
+          <t>Meter Service</t>
         </is>
       </c>
       <c r="D100" s="2" t="inlineStr">
@@ -6294,7 +6294,7 @@
       </c>
       <c r="M100" s="2" t="inlineStr">
         <is>
-          <t>General Repair scheduled or reactive task 099</t>
+          <t>Meter Service scheduled or reactive task 099</t>
         </is>
       </c>
     </row>
@@ -6311,7 +6311,7 @@
       </c>
       <c r="C101" s="2" t="inlineStr">
         <is>
-          <t>General Repair</t>
+          <t>Meter Service</t>
         </is>
       </c>
       <c r="D101" s="2" t="inlineStr">
@@ -6347,7 +6347,7 @@
       </c>
       <c r="M101" s="2" t="inlineStr">
         <is>
-          <t>General Repair scheduled or reactive task 100</t>
+          <t>Meter Service scheduled or reactive task 100</t>
         </is>
       </c>
     </row>
@@ -6364,7 +6364,7 @@
       </c>
       <c r="C102" s="2" t="inlineStr">
         <is>
-          <t>HVAC</t>
+          <t>Leak Repair</t>
         </is>
       </c>
       <c r="D102" s="2" t="inlineStr">
@@ -6402,7 +6402,7 @@
       </c>
       <c r="M102" s="2" t="inlineStr">
         <is>
-          <t>HVAC scheduled or reactive task 101</t>
+          <t>Leak Repair scheduled or reactive task 101</t>
         </is>
       </c>
     </row>
@@ -6419,7 +6419,7 @@
       </c>
       <c r="C103" s="2" t="inlineStr">
         <is>
-          <t>HVAC</t>
+          <t>Leak Repair</t>
         </is>
       </c>
       <c r="D103" s="2" t="inlineStr">
@@ -6457,7 +6457,7 @@
       </c>
       <c r="M103" s="2" t="inlineStr">
         <is>
-          <t>HVAC scheduled or reactive task 102</t>
+          <t>Leak Repair scheduled or reactive task 102</t>
         </is>
       </c>
     </row>
@@ -6474,7 +6474,7 @@
       </c>
       <c r="C104" s="2" t="inlineStr">
         <is>
-          <t>HVAC</t>
+          <t>Leak Repair</t>
         </is>
       </c>
       <c r="D104" s="2" t="inlineStr">
@@ -6510,7 +6510,7 @@
       </c>
       <c r="M104" s="2" t="inlineStr">
         <is>
-          <t>HVAC scheduled or reactive task 103</t>
+          <t>Leak Repair scheduled or reactive task 103</t>
         </is>
       </c>
     </row>
@@ -6527,7 +6527,7 @@
       </c>
       <c r="C105" s="2" t="inlineStr">
         <is>
-          <t>HVAC</t>
+          <t>Leak Repair</t>
         </is>
       </c>
       <c r="D105" s="2" t="inlineStr">
@@ -6563,7 +6563,7 @@
       </c>
       <c r="M105" s="2" t="inlineStr">
         <is>
-          <t>HVAC scheduled or reactive task 104</t>
+          <t>Leak Repair scheduled or reactive task 104</t>
         </is>
       </c>
     </row>
@@ -6580,7 +6580,7 @@
       </c>
       <c r="C106" s="2" t="inlineStr">
         <is>
-          <t>Electrical</t>
+          <t>Valve Repair</t>
         </is>
       </c>
       <c r="D106" s="2" t="inlineStr">
@@ -6616,7 +6616,7 @@
       </c>
       <c r="M106" s="2" t="inlineStr">
         <is>
-          <t>Electrical scheduled or reactive task 105</t>
+          <t>Valve Repair scheduled or reactive task 105</t>
         </is>
       </c>
     </row>
@@ -6633,7 +6633,7 @@
       </c>
       <c r="C107" s="2" t="inlineStr">
         <is>
-          <t>Electrical</t>
+          <t>Valve Repair</t>
         </is>
       </c>
       <c r="D107" s="2" t="inlineStr">
@@ -6671,7 +6671,7 @@
       </c>
       <c r="M107" s="2" t="inlineStr">
         <is>
-          <t>Electrical scheduled or reactive task 106</t>
+          <t>Valve Repair scheduled or reactive task 106</t>
         </is>
       </c>
     </row>
@@ -6688,7 +6688,7 @@
       </c>
       <c r="C108" s="2" t="inlineStr">
         <is>
-          <t>Electrical</t>
+          <t>Valve Repair</t>
         </is>
       </c>
       <c r="D108" s="2" t="inlineStr">
@@ -6726,7 +6726,7 @@
       </c>
       <c r="M108" s="2" t="inlineStr">
         <is>
-          <t>Electrical scheduled or reactive task 107</t>
+          <t>Valve Repair scheduled or reactive task 107</t>
         </is>
       </c>
     </row>
@@ -6743,7 +6743,7 @@
       </c>
       <c r="C109" s="2" t="inlineStr">
         <is>
-          <t>Electrical</t>
+          <t>Valve Repair</t>
         </is>
       </c>
       <c r="D109" s="2" t="inlineStr">
@@ -6779,7 +6779,7 @@
       </c>
       <c r="M109" s="2" t="inlineStr">
         <is>
-          <t>Electrical scheduled or reactive task 108</t>
+          <t>Valve Repair scheduled or reactive task 108</t>
         </is>
       </c>
     </row>
@@ -6796,7 +6796,7 @@
       </c>
       <c r="C110" s="2" t="inlineStr">
         <is>
-          <t>Plumbing</t>
+          <t>Pipe Replacement</t>
         </is>
       </c>
       <c r="D110" s="2" t="inlineStr">
@@ -6828,7 +6828,7 @@
       </c>
       <c r="M110" s="2" t="inlineStr">
         <is>
-          <t>Plumbing scheduled or reactive task 109</t>
+          <t>Pipe Replacement scheduled or reactive task 109</t>
         </is>
       </c>
     </row>
@@ -6845,7 +6845,7 @@
       </c>
       <c r="C111" s="2" t="inlineStr">
         <is>
-          <t>Plumbing</t>
+          <t>Pipe Replacement</t>
         </is>
       </c>
       <c r="D111" s="2" t="inlineStr">
@@ -6881,7 +6881,7 @@
       </c>
       <c r="M111" s="2" t="inlineStr">
         <is>
-          <t>Plumbing scheduled or reactive task 110</t>
+          <t>Pipe Replacement scheduled or reactive task 110</t>
         </is>
       </c>
     </row>
@@ -6898,7 +6898,7 @@
       </c>
       <c r="C112" s="2" t="inlineStr">
         <is>
-          <t>Plumbing</t>
+          <t>Pipe Replacement</t>
         </is>
       </c>
       <c r="D112" s="2" t="inlineStr">
@@ -6936,7 +6936,7 @@
       </c>
       <c r="M112" s="2" t="inlineStr">
         <is>
-          <t>Plumbing scheduled or reactive task 111</t>
+          <t>Pipe Replacement scheduled or reactive task 111</t>
         </is>
       </c>
     </row>
@@ -6953,7 +6953,7 @@
       </c>
       <c r="C113" s="2" t="inlineStr">
         <is>
-          <t>Plumbing</t>
+          <t>Pipe Replacement</t>
         </is>
       </c>
       <c r="D113" s="2" t="inlineStr">
@@ -6991,7 +6991,7 @@
       </c>
       <c r="M113" s="2" t="inlineStr">
         <is>
-          <t>Plumbing scheduled or reactive task 112</t>
+          <t>Pipe Replacement scheduled or reactive task 112</t>
         </is>
       </c>
     </row>
@@ -7008,7 +7008,7 @@
       </c>
       <c r="C114" s="2" t="inlineStr">
         <is>
-          <t>Fire Safety</t>
+          <t>Pump Service</t>
         </is>
       </c>
       <c r="D114" s="2" t="inlineStr">
@@ -7044,7 +7044,7 @@
       </c>
       <c r="M114" s="2" t="inlineStr">
         <is>
-          <t>Fire Safety scheduled or reactive task 113</t>
+          <t>Pump Service scheduled or reactive task 113</t>
         </is>
       </c>
     </row>
@@ -7061,7 +7061,7 @@
       </c>
       <c r="C115" s="2" t="inlineStr">
         <is>
-          <t>Fire Safety</t>
+          <t>Pump Service</t>
         </is>
       </c>
       <c r="D115" s="2" t="inlineStr">
@@ -7097,7 +7097,7 @@
       </c>
       <c r="M115" s="2" t="inlineStr">
         <is>
-          <t>Fire Safety scheduled or reactive task 114</t>
+          <t>Pump Service scheduled or reactive task 114</t>
         </is>
       </c>
     </row>
@@ -7114,7 +7114,7 @@
       </c>
       <c r="C116" s="2" t="inlineStr">
         <is>
-          <t>Fire Safety</t>
+          <t>Pump Service</t>
         </is>
       </c>
       <c r="D116" s="2" t="inlineStr">
@@ -7150,7 +7150,7 @@
       </c>
       <c r="M116" s="2" t="inlineStr">
         <is>
-          <t>Fire Safety scheduled or reactive task 115</t>
+          <t>Pump Service scheduled or reactive task 115</t>
         </is>
       </c>
     </row>
@@ -7167,7 +7167,7 @@
       </c>
       <c r="C117" s="2" t="inlineStr">
         <is>
-          <t>Fire Safety</t>
+          <t>Pump Service</t>
         </is>
       </c>
       <c r="D117" s="2" t="inlineStr">
@@ -7205,7 +7205,7 @@
       </c>
       <c r="M117" s="2" t="inlineStr">
         <is>
-          <t>Fire Safety scheduled or reactive task 116</t>
+          <t>Pump Service scheduled or reactive task 116</t>
         </is>
       </c>
     </row>
@@ -7222,7 +7222,7 @@
       </c>
       <c r="C118" s="2" t="inlineStr">
         <is>
-          <t>General Repair</t>
+          <t>Meter Service</t>
         </is>
       </c>
       <c r="D118" s="2" t="inlineStr">
@@ -7260,7 +7260,7 @@
       </c>
       <c r="M118" s="2" t="inlineStr">
         <is>
-          <t>General Repair scheduled or reactive task 117</t>
+          <t>Meter Service scheduled or reactive task 117</t>
         </is>
       </c>
     </row>
@@ -7277,7 +7277,7 @@
       </c>
       <c r="C119" s="2" t="inlineStr">
         <is>
-          <t>General Repair</t>
+          <t>Meter Service</t>
         </is>
       </c>
       <c r="D119" s="2" t="inlineStr">
@@ -7313,7 +7313,7 @@
       </c>
       <c r="M119" s="2" t="inlineStr">
         <is>
-          <t>General Repair scheduled or reactive task 118</t>
+          <t>Meter Service scheduled or reactive task 118</t>
         </is>
       </c>
     </row>
@@ -7330,7 +7330,7 @@
       </c>
       <c r="C120" s="2" t="inlineStr">
         <is>
-          <t>General Repair</t>
+          <t>Meter Service</t>
         </is>
       </c>
       <c r="D120" s="2" t="inlineStr">
@@ -7366,7 +7366,7 @@
       </c>
       <c r="M120" s="2" t="inlineStr">
         <is>
-          <t>General Repair scheduled or reactive task 119</t>
+          <t>Meter Service scheduled or reactive task 119</t>
         </is>
       </c>
     </row>
@@ -7383,7 +7383,7 @@
       </c>
       <c r="C121" s="2" t="inlineStr">
         <is>
-          <t>General Repair</t>
+          <t>Meter Service</t>
         </is>
       </c>
       <c r="D121" s="2" t="inlineStr">
@@ -7419,7 +7419,7 @@
       </c>
       <c r="M121" s="2" t="inlineStr">
         <is>
-          <t>General Repair scheduled or reactive task 120</t>
+          <t>Meter Service scheduled or reactive task 120</t>
         </is>
       </c>
     </row>
@@ -7477,7 +7477,7 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>HVAC</t>
+          <t>Leak Repair</t>
         </is>
       </c>
       <c r="C2" s="2" t="n">
@@ -7497,7 +7497,7 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>HVAC</t>
+          <t>Leak Repair</t>
         </is>
       </c>
       <c r="C3" s="2" t="n">
@@ -7517,7 +7517,7 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>HVAC</t>
+          <t>Leak Repair</t>
         </is>
       </c>
       <c r="C4" s="2" t="n">
@@ -7537,7 +7537,7 @@
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>HVAC</t>
+          <t>Leak Repair</t>
         </is>
       </c>
       <c r="C5" s="2" t="n">
@@ -7557,7 +7557,7 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>Electrical</t>
+          <t>Valve Repair</t>
         </is>
       </c>
       <c r="C6" s="2" t="n">
@@ -7577,7 +7577,7 @@
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>Electrical</t>
+          <t>Valve Repair</t>
         </is>
       </c>
       <c r="C7" s="2" t="n">
@@ -7597,7 +7597,7 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>Electrical</t>
+          <t>Valve Repair</t>
         </is>
       </c>
       <c r="C8" s="2" t="n">
@@ -7617,7 +7617,7 @@
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>Electrical</t>
+          <t>Valve Repair</t>
         </is>
       </c>
       <c r="C9" s="2" t="n">
@@ -7823,7 +7823,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F3"/>
+  <dimension ref="A1:F6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
@@ -7869,36 +7869,90 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
+          <t>Step 1</t>
+        </is>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>EXCEL - CHAT ONLY</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>EXCEL - CHAT ONLY:
+For the untouched 120-row Northstar Water Services baseline dashboard at 2026-09-30, All selectors, return a presentation evidence table: six KPIs, backlog by site, status and job-category counts, unassigned backlog and relevant source references. Do not use the refresh-test copy or infer service disruption, safety risk, causes or savings.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
           <t>Step 2</t>
         </is>
       </c>
-      <c r="B2" s="2" t="inlineStr">
+      <c r="B3" s="2" t="inlineStr">
         <is>
           <t>WORD COPILOT</t>
         </is>
       </c>
-      <c r="C2" s="2" t="inlineStr">
+      <c r="C3" s="2" t="inlineStr">
         <is>
           <t>WORD COPILOT:
 Using this verified 120-row Northstar maintenance snapshot, draft an eight-slide management presentation brief. For each slide give one claim headline, supporting measure/chart, source/date/scope, limitation and speaker note. Structure: overview, portfolio, site backlog, status/category mix, SLA/overdue, assignment/capacity, proposed actions/trade-offs, decision/next review. Do not invent causes, savings, approval or future dates; use UNKNOWN when absent.</t>
         </is>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" s="2" t="inlineStr">
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>Step 3</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>WORD COPILOT</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>WORD COPILOT:
+Review this eight-slide Northstar Water Services brief against the supplied baseline evidence. Check each headline has a supporting value, correct units, source/date/scope and an explicit limitation. Rewrite unsupported claims as questions or proposed actions. Do not change verified figures or invent approvals.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
         <is>
           <t>Step 4</t>
         </is>
       </c>
-      <c r="B3" s="2" t="inlineStr">
+      <c r="B5" s="2" t="inlineStr">
         <is>
           <t>POWERPOINT COPILOT</t>
         </is>
       </c>
-      <c r="C3" s="2" t="inlineStr">
+      <c r="C5" s="2" t="inlineStr">
         <is>
           <t>POWERPOINT COPILOT:
 @maintenance-reporting Create or update an eight-slide management presentation from the selected Northstar_Presentation_Brief.docx. Follow the existing white/navy/blue template. One evidence-based message per slide, short visible text, charts or tables for numerical evidence, source/as-at/scope in notes, and a final decision request. Keep values exact, and label all next actions as proposed. Do not add extra slides or invented facts.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>Step 6</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>POWERPOINT COPILOT</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>POWERPOINT COPILOT:
+Audit the eight-slide Northstar Water Services management draft against the selected presentation brief and evidence register. Confirm baseline 120, source notes, chart labels and units, correct backlog exclusions and proposed-action wording. List needed corrections and preserve slide count; do not claim Excel charts update automatically.</t>
         </is>
       </c>
     </row>
@@ -8275,7 +8329,7 @@
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>HVAC</t>
+          <t>Leak Repair</t>
         </is>
       </c>
       <c r="B25" s="2">
@@ -8288,7 +8342,7 @@
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>Electrical</t>
+          <t>Valve Repair</t>
         </is>
       </c>
       <c r="B26" s="2">
@@ -8301,7 +8355,7 @@
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>Plumbing</t>
+          <t>Pipe Replacement</t>
         </is>
       </c>
       <c r="B27" s="2">
@@ -8314,7 +8368,7 @@
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>Fire Safety</t>
+          <t>Pump Service</t>
         </is>
       </c>
       <c r="B28" s="2">
@@ -8327,7 +8381,7 @@
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>General Repair</t>
+          <t>Meter Service</t>
         </is>
       </c>
       <c r="B29" s="2">
@@ -8494,7 +8548,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>HVAC</t>
+          <t>Leak Repair</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -8516,7 +8570,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Electrical</t>
+          <t>Valve Repair</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -8538,7 +8592,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Plumbing</t>
+          <t>Pipe Replacement</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -8560,7 +8614,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Fire Safety</t>
+          <t>Pump Service</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -8582,7 +8636,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>General Repair</t>
+          <t>Meter Service</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
